--- a/src/product_data_results.xlsx
+++ b/src/product_data_results.xlsx
@@ -1,121 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/godfather/Library/CloudStorage/OneDrive-Personal/MacProjects/hafele_web_scraping_without_docker/updatedWebScrapingProject/src/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCAF137D-6766-7C46-B06C-D851A3F0DD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
-  <si>
-    <t>stockCode</t>
-  </si>
-  <si>
-    <t>stock_amount</t>
-  </si>
-  <si>
-    <t>stok_durumu</t>
-  </si>
-  <si>
-    <t>kdv_haric_satis_fiyati</t>
-  </si>
-  <si>
-    <t>kdv_haric_net_fiyat</t>
-  </si>
-  <si>
-    <t>kdv_haric_tavsiye_edilen_perakende_fiyat</t>
-  </si>
-  <si>
-    <t>900.70.061</t>
-  </si>
-  <si>
-    <t>stokta mevcut</t>
-  </si>
-  <si>
-    <t>1.449,17 TL
-#  Adet (ADT)</t>
-  </si>
-  <si>
-    <t>1.552,68 TL
-#  Adet (ADT)</t>
-  </si>
-  <si>
-    <t>1.035,12 TL
-#  Adet (ADT)</t>
-  </si>
-  <si>
-    <t>900.70.062</t>
-  </si>
-  <si>
-    <t>1.607,50 TL
-#  Adet (ADT)</t>
-  </si>
-  <si>
-    <t>1.722,32 TL
-#  Adet (ADT)</t>
-  </si>
-  <si>
-    <t>1.148,21 TL
-#  Adet (ADT)</t>
-  </si>
-  <si>
-    <t>900.70.063</t>
-  </si>
-  <si>
-    <t>900.70.066</t>
-  </si>
-  <si>
-    <t>900.70.068</t>
-  </si>
-  <si>
-    <t>1.649,17 TL
-#  Adet (ADT)</t>
-  </si>
-  <si>
-    <t>1.766,96 TL
-#  Adet (ADT)</t>
-  </si>
-  <si>
-    <t>1.177,98 TL
-#  Adet (ADT)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -130,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -454,135 +420,76 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.5" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>stockCode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>stock_amount</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>stok_durumu</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>kdv_haric_satis_fiyati</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kdv_haric_net_fiyat</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>kdv_haric_tavsiye_edilen_perakende_fiyat</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5">
-        <v>133</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>900.78.409</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>209</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.244,84 TL
+#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.244,84 TL</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1.867,26 TL
+#  Set (Set)</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/src/product_data_results.xlsx
+++ b/src/product_data_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,49 +446,2238 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>kdv_haric_tavsiye_edilen_perakende_fiyat</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kdv_haric_tavsiye_edilen_perakende_unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>kdv_haric_net_fiyat</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>kdv_haric_net_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>kdv_haric_satis_fiyati</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>kdv_haric_net_fiyat</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>kdv_haric_tavsiye_edilen_perakende_fiyat</t>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>kdv_haric_satis_units</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>900.78.409</t>
+          <t>900.70.061</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>209</v>
+        <v>22</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Group Product</t>
+          <t>stokta mevcut</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.244,84 TL
-#  Set (Set)</t>
+          <t>1.449,17 TL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.244,84 TL</t>
+          <t>#  Adet (ADT)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.867,26 TL
-#  Set (Set)</t>
+          <t>1.035,12 TL</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1.552,68 TL</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>900.70.062</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>stokta mevcut</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1.607,50 TL</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1.148,21 TL</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1.722,32 TL</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>900.70.066</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>133</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>stokta mevcut</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1.607,50 TL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1.148,21 TL</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1.722,32 TL</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>900.70.068</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>stokta mevcut</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1.649,17 TL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1.177,98 TL</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1.766,96 TL</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>900.70.382</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>26</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>stokta mevcut</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>882,50 TL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>678,85 TL</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1.018,27 TL</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>900.70.383</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>312</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>stokta mevcut</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>849,17 TL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>653,21 TL</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>979,81 TL</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>900.70.384</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>52</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>stokta mevcut</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>915,83 TL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>704,49 TL</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1.056,73 TL</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>900.70.386</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>194</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>stokta mevcut</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>731,63 TL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>562,79 TL</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>844,18 TL</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>900.70.391</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Urun hafele.com.tr de bulunmuyor</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>900.70.388</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>stokta mevcut</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>915,83 TL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>704,49 TL</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1.056,73 TL</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>900.70.063</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>stokta mevcut</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.449,17 TL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1.035,12 TL</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1.552,68 TL</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>900.70.393</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>355</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>stokta mevcut</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>932,50 TL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>717,31 TL</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1.075,96 TL</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>900.70.394</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>29</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>stokta mevcut</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.015,83 TL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>781,41 TL</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1.172,12 TL</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>900.70.396</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>44</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>stokta mevcut</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>833,29 TL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>640,99 TL</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>961,49 TL</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>900.70.398</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>stokta mevcut</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>999,17 TL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>768,59 TL</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1.152,88 TL</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>900.78.214</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>39</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1.544,13 TL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1.102,95 TL</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1.654,42 TL</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>900.78.215</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>124</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1.544,13 TL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1.102,95 TL</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.654,42 TL</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>900.78.217</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fiyat talep üzerine bildirilir</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fiyat talep üzerine bildirilir</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Fiyat talep üzerine bildirilir</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>900.70.392</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>11</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>stokta mevcut</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>982,50 TL</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>755,77 TL</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1.133,65 TL</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>#  Adet (ADT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>900.78.216</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>39</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1.544,13 TL</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1.102,95 TL</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1.654,42 TL</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>900.78.218</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>39</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1.910,79 TL</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1.364,85 TL</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2.047,28 TL</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>900.78.322</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>885</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1.540,79 TL</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1.185,22 TL</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1.777,84 TL</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>900.78.321</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>696</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1.540,79 TL</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1.185,22 TL</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1.777,84 TL</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>900.78.219</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>64</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1.910,79 TL</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1.364,85 TL</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2.047,28 TL</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>900.78.324</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1137</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1.699,96 TL</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1.307,66 TL</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1.961,49 TL</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>900.78.323</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>616</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1.693,29 TL</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1.302,53 TL</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1.953,80 TL</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>900.78.325</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>570</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1.699,96 TL</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1.307,66 TL</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1.961,49 TL</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>900.78.327</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>66</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1.699,96 TL</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1.307,66 TL</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>1.961,49 TL</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>900.78.326</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>566</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1.868,29 TL</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1.437,15 TL</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2.155,72 TL</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>900.78.328</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>15</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1.699,96 TL</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1.307,66 TL</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>1.961,49 TL</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>900.78.333</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>310</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1.904,13 TL</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1.464,71 TL</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2.197,07 TL</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>900.78.329</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>66</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1.868,29 TL</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1.437,15 TL</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2.155,72 TL</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>900.78.334</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>125</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1.904,13 TL</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1.464,71 TL</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2.197,07 TL</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>900.78.336</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>373</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1.665,79 TL</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1.281,38 TL</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1.922,07 TL</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>900.78.337</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>373</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1.665,79 TL</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1.281,38 TL</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>1.922,07 TL</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>900.78.339</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>891</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1.833,29 TL</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1.410,22 TL</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2.115,34 TL</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>900.78.335</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>141</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2.091,63 TL</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1.608,94 TL</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2.413,41 TL</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>900.78.338</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>373</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1.818,29 TL</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1.398,69 TL</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2.098,03 TL</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>900.78.340</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>570</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1.833,29 TL</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1.410,22 TL</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2.115,34 TL</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>900.78.341</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>566</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2.001,63 TL</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1.539,71 TL</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2.309,57 TL</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>900.78.343</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>15</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1.833,29 TL</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1.410,22 TL</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2.115,34 TL</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>900.78.342</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>318</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1.833,29 TL</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1.410,22 TL</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2.115,34 TL</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>900.78.344</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>285</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2.001,63 TL</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1.539,71 TL</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2.309,57 TL</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>900.78.347</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>381</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1.823,29 TL</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1.402,53 TL</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2.103,80 TL</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>900.78.345</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>461</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1.669,96 TL</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1.284,58 TL</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1.926,87 TL</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>900.78.346</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>52</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1.669,96 TL</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1.284,58 TL</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>1.926,87 TL</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>900.78.348</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>723</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1.838,29 TL</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1.414,07 TL</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2.121,11 TL</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>900.78.349</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>108</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1.838,29 TL</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1.414,07 TL</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2.121,11 TL</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>900.78.350</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>723</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2.006,63 TL</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1.543,56 TL</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2.315,34 TL</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>900.78.351</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>51</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Group Product</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1.803,29 TL</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1.387,15 TL</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2.080,72 TL</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>#  Set (Set)</t>
         </is>
       </c>
     </row>
